--- a/artfynd/A 7958-2022 artfynd.xlsx
+++ b/artfynd/A 7958-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7958-2022 artfynd.xlsx
+++ b/artfynd/A 7958-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111298906</v>
+        <v>111298694</v>
       </c>
       <c r="B2" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817418.2711159306</v>
+        <v>817132</v>
       </c>
       <c r="R2" t="n">
-        <v>7527277.119381912</v>
+        <v>7527179</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,19 +746,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111299032</v>
+        <v>111298793</v>
       </c>
       <c r="B3" t="n">
-        <v>95538</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817696.7934497184</v>
+        <v>817158</v>
       </c>
       <c r="R3" t="n">
-        <v>7527086.718570219</v>
+        <v>7527296</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -868,19 +847,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111298754</v>
+        <v>111298906</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817115.4577740564</v>
+        <v>817418</v>
       </c>
       <c r="R4" t="n">
-        <v>7527267.066006545</v>
+        <v>7527277</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -984,19 +948,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111298764</v>
+        <v>111298703</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817158.0421085733</v>
+        <v>817132</v>
       </c>
       <c r="R5" t="n">
-        <v>7527295.647014287</v>
+        <v>7527179</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1100,19 +1049,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111298720</v>
+        <v>111298764</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817074.3486132142</v>
+        <v>817158</v>
       </c>
       <c r="R6" t="n">
-        <v>7527270.496540484</v>
+        <v>7527296</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1216,19 +1150,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111298703</v>
+        <v>111298894</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>817132.6591581996</v>
+        <v>817418</v>
       </c>
       <c r="R7" t="n">
-        <v>7527179.418402886</v>
+        <v>7527277</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1332,19 +1251,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,43 +1281,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111298466</v>
+        <v>111298482</v>
       </c>
       <c r="B8" t="n">
-        <v>95538</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1416,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>817344.8428052007</v>
+        <v>817318</v>
       </c>
       <c r="R8" t="n">
-        <v>7526988.185979445</v>
+        <v>7527066</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1449,19 +1352,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,44 +1375,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka, Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111298826</v>
+        <v>111298952</v>
       </c>
       <c r="B9" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817232.9614453327</v>
+        <v>817454</v>
       </c>
       <c r="R9" t="n">
-        <v>7527282.530812319</v>
+        <v>7527245</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1565,19 +1453,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111298793</v>
+        <v>111298720</v>
       </c>
       <c r="B10" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817158.0421085733</v>
+        <v>817074</v>
       </c>
       <c r="R10" t="n">
-        <v>7527295.647014287</v>
+        <v>7527271</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1681,19 +1554,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,43 +1584,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111298884</v>
+        <v>111298754</v>
       </c>
       <c r="B11" t="n">
-        <v>95538</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1765,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>817296.9808386452</v>
+        <v>817115</v>
       </c>
       <c r="R11" t="n">
-        <v>7527289.56488536</v>
+        <v>7527267</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1798,19 +1655,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111298742</v>
+        <v>111298814</v>
       </c>
       <c r="B12" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1881,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>817068.1324238419</v>
+        <v>817158</v>
       </c>
       <c r="R12" t="n">
-        <v>7527277.409662396</v>
+        <v>7527296</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1914,19 +1756,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111298952</v>
+        <v>111298491</v>
       </c>
       <c r="B13" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,26 +1797,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1997,13 +1825,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>817454.7552061283</v>
+        <v>817271</v>
       </c>
       <c r="R13" t="n">
-        <v>7527245.516410586</v>
+        <v>7527067</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2030,28 +1858,17 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2063,49 +1880,45 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka, Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111298814</v>
+        <v>111298466</v>
       </c>
       <c r="B14" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2113,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>817158.0421085733</v>
+        <v>817345</v>
       </c>
       <c r="R14" t="n">
-        <v>7527295.647014287</v>
+        <v>7526988</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2146,19 +1959,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,49 +1982,45 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka, Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111298894</v>
+        <v>111298884</v>
       </c>
       <c r="B15" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2229,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817418.2711159306</v>
+        <v>817297</v>
       </c>
       <c r="R15" t="n">
-        <v>7527277.119381912</v>
+        <v>7527289</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2262,19 +2061,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,42 +2091,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111298694</v>
+        <v>111299032</v>
       </c>
       <c r="B16" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2345,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817132.6591581996</v>
+        <v>817696</v>
       </c>
       <c r="R16" t="n">
-        <v>7527179.418402886</v>
+        <v>7527087</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2378,19 +2163,9 @@
           <t>2023-08-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 7958-2022 artfynd.xlsx
+++ b/artfynd/A 7958-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298906</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298703</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298764</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298894</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298482</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298952</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298720</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298754</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298814</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298491</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298466</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298884</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,8 +2265,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111299032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>